--- a/output/spreadsheet/pyg_ltd_2026.xlsx
+++ b/output/spreadsheet/pyg_ltd_2026.xlsx
@@ -703,7 +703,7 @@
     <row r="3" ht="12" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Shopify daily average | Actualizado: 31/07/2026 09:47 h</t>
+          <t>Shopify daily average | Actualizado: 31/07/2026 12:25 h</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -949,7 +949,7 @@
         </is>
       </c>
     </row>
-    <row r="7" hidden="1" outlineLevel="3" ht="12" customHeight="1">
+    <row r="7" ht="12" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">      GB</t>
@@ -1015,7 +1015,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="12" customHeight="1">
+    <row r="8" hidden="1" outlineLevel="3" ht="12" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">        avg/day</t>
@@ -1593,7 +1593,7 @@
         <v>1980.34</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>2111.42</v>
+        <v>2120.24</v>
       </c>
       <c r="K18" s="4" t="n"/>
       <c r="L18" s="4" t="n"/>
@@ -3247,7 +3247,7 @@
         <v>37841.32</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>35729.9</v>
+        <v>35721.08</v>
       </c>
       <c r="K49" s="4" t="n"/>
       <c r="L49" s="4" t="n"/>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31T07:47:59Z</t>
+          <t>2026-07-31T10:25:26Z</t>
         </is>
       </c>
     </row>
@@ -3750,7 +3750,7 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>18341.96</v>
+        <v>18441.88</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>1</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>18341.96</v>
+        <v>18441.88</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
